--- a/fuentes_datos.xlsx
+++ b/fuentes_datos.xlsx
@@ -12,14 +12,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fuentes actuales'!$A$1:$G$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fuentes externas'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fuentes externas'!$A$1:$G$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="155">
   <si>
     <t>Fuente</t>
   </si>
@@ -415,6 +415,60 @@
   </si>
   <si>
     <t>https://www.inegi.org.mx/programas/enaproce/2018/</t>
+  </si>
+  <si>
+    <t>Microdatos de Censos Económicos (Laboratorio de Microdatos)</t>
+  </si>
+  <si>
+    <t>Economía de CADA establecimiento: ingresos, gastos, remuneraciones, activos fijos y personal exacto (censos 2014/2019/2024). No públicos: acceso gratuito para posgrado/investigadores vía solicitud a microdatos@inegi.org.mx (CV + aval del director de tesis), presencial o procesamiento remoto; solo salen resultados agregados revisados por confidencialidad. La CLEE nace de estos censos → comparte identificador con el panel DENUE. Iniciar trámite con anticipación (tarda).</t>
+  </si>
+  <si>
+    <t>Establecimiento (dentro del entorno INEGI)</t>
+  </si>
+  <si>
+    <t>Candidata de alto valor — requiere trámite; complemento, no bloqueante</t>
+  </si>
+  <si>
+    <t>https://www.inegi.org.mx/microdatos/</t>
+  </si>
+  <si>
+    <t>SIEM (Sistema de Información Empresarial Mexicano)</t>
+  </si>
+  <si>
+    <t>Secretaría de Economía</t>
+  </si>
+  <si>
+    <t>Directorio de empresas registradas vía cámaras empresariales: contacto y giro, SIN información financiera y con cobertura sesgada (solo afiliadas). No aporta sobre lo que ya da DENUE.</t>
+  </si>
+  <si>
+    <t>Empresa (registro)</t>
+  </si>
+  <si>
+    <t>Continua</t>
+  </si>
+  <si>
+    <t>Descartada — sin datos económicos, cobertura sesgada</t>
+  </si>
+  <si>
+    <t>https://siem.economia.gob.mx/</t>
+  </si>
+  <si>
+    <t>Estados financieros de emisoras (BMV / BIVA)</t>
+  </si>
+  <si>
+    <t>BMV / BIVA / CNBV</t>
+  </si>
+  <si>
+    <t>Estados financieros completos, pero solo de ~140 empresas listadas en bolsa — irrelevante para micronegocios; el segmento no se traslapa con el objeto de estudio.</t>
+  </si>
+  <si>
+    <t>Empresa (solo emisoras)</t>
+  </si>
+  <si>
+    <t>Descartada — segmento no comparable</t>
+  </si>
+  <si>
+    <t>https://www.bmv.com.mx/</t>
   </si>
   <si>
     <t>Proyecciones de población municipal</t>
@@ -924,7 +978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.7109375" customWidth="1"/>
@@ -1378,16 +1432,16 @@
         <v>132</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>133</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>135</v>
@@ -1396,8 +1450,77 @@
         <v>136</v>
       </c>
     </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G23"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -1418,6 +1541,9 @@
     <hyperlink ref="G18" r:id="rId17"/>
     <hyperlink ref="G19" r:id="rId18"/>
     <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
+    <hyperlink ref="G23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/fuentes_datos.xlsx
+++ b/fuentes_datos.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victoryeudicastillo/Projects/tesis/etl-core/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5B989B-3F0E-084E-B81E-39806162AAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fuentes actuales" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fuentes actuales'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fuentes externas'!$A$1:$G$23</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -489,8 +495,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,7 +521,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -525,6 +531,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF305496"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,7 +574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -567,19 +585,39 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -617,7 +655,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -651,6 +689,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -685,9 +724,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -860,20 +900,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="72.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" customWidth="1"/>
-    <col min="6" max="6" width="34.7109375" customWidth="1"/>
-    <col min="7" max="7" width="46.7109375" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="72.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" customWidth="1"/>
+    <col min="6" max="6" width="34.6640625" customWidth="1"/>
+    <col min="7" max="7" width="46.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -896,7 +936,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -919,7 +959,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -942,7 +982,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -966,31 +1006,31 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1"/>
-    <hyperlink ref="G3" r:id="rId2"/>
-    <hyperlink ref="G4" r:id="rId3"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="72.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" customWidth="1"/>
-    <col min="6" max="6" width="34.7109375" customWidth="1"/>
-    <col min="7" max="7" width="46.7109375" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="72.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" customWidth="1"/>
+    <col min="6" max="6" width="34.6640625" customWidth="1"/>
+    <col min="7" max="7" width="46.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1013,30 +1053,30 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>33</v>
       </c>
@@ -1059,7 +1099,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
@@ -1082,7 +1122,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
@@ -1105,7 +1145,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>50</v>
       </c>
@@ -1128,30 +1168,30 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>62</v>
       </c>
@@ -1174,7 +1214,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>68</v>
       </c>
@@ -1197,7 +1237,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>74</v>
       </c>
@@ -1220,7 +1260,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>80</v>
       </c>
@@ -1243,30 +1283,30 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>93</v>
       </c>
@@ -1289,7 +1329,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>100</v>
       </c>
@@ -1312,7 +1352,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>107</v>
       </c>
@@ -1335,7 +1375,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
@@ -1358,7 +1398,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>115</v>
       </c>
@@ -1381,7 +1421,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>121</v>
       </c>
@@ -1404,7 +1444,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>127</v>
       </c>
@@ -1427,7 +1467,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" ht="96" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
@@ -1450,7 +1490,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>137</v>
       </c>
@@ -1473,7 +1513,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>144</v>
       </c>
@@ -1496,7 +1536,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>150</v>
       </c>
@@ -1520,30 +1560,30 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G23"/>
+  <autoFilter ref="A1:G23" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1"/>
-    <hyperlink ref="G3" r:id="rId2"/>
-    <hyperlink ref="G4" r:id="rId3"/>
-    <hyperlink ref="G5" r:id="rId4"/>
-    <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-    <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G23" r:id="rId22"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="G10" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="G11" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="G14" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="G15" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="G16" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="G17" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="G18" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="G19" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="G20" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="G21" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="G22" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="G23" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
